--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1300,6 +1300,1545 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132474622</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>656406</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6631060</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132474647</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>656483</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6630977</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132474646</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>656437</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6630978</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132474627</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>656415</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6630978</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132474614</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>656401</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6631017</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132474620</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96419</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>656419</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6631021</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132474615</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>656402</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6631028</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132474611</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>656421</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6631001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132474626</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>656413</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6630982</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132474618</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>656420</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6631034</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132474610</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>656435</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6630991</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132474616</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>656414</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6631037</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132474621</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96417</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>656417</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6631023</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132474628</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106222</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>656409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6630987</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -1744,10 +1744,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132474614</v>
+        <v>132474620</v>
       </c>
       <c r="B11" t="n">
-        <v>101304</v>
+        <v>96419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656401</v>
+        <v>656419</v>
       </c>
       <c r="R11" t="n">
-        <v>6631017</v>
+        <v>6631021</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132474620</v>
+        <v>132474614</v>
       </c>
       <c r="B12" t="n">
-        <v>96419</v>
+        <v>101304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2666</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656419</v>
+        <v>656401</v>
       </c>
       <c r="R12" t="n">
-        <v>6631021</v>
+        <v>6631017</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2400,54 +2400,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132474610</v>
+        <v>132474616</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656435</v>
+        <v>656414</v>
       </c>
       <c r="R17" t="n">
-        <v>6630991</v>
+        <v>6631037</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,45 +2507,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132474616</v>
+        <v>132474610</v>
       </c>
       <c r="B18" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656414</v>
+        <v>656435</v>
       </c>
       <c r="R18" t="n">
-        <v>6631037</v>
+        <v>6630991</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -1302,32 +1302,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132474622</v>
+        <v>132474647</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>101312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656406</v>
+        <v>656483</v>
       </c>
       <c r="R7" t="n">
-        <v>6631060</v>
+        <v>6630977</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,32 +1409,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132474647</v>
+        <v>132474622</v>
       </c>
       <c r="B8" t="n">
-        <v>101304</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656483</v>
+        <v>656406</v>
       </c>
       <c r="R8" t="n">
-        <v>6630977</v>
+        <v>6631060</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1489,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,51 +1521,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132474646</v>
+        <v>132474627</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>4781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656437</v>
+        <v>656415</v>
       </c>
       <c r="R9" t="n">
         <v>6630978</v>
@@ -1600,7 +1591,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1601,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,42 +1628,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132474627</v>
+        <v>132474646</v>
       </c>
       <c r="B10" t="n">
-        <v>4781</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656415</v>
+        <v>656437</v>
       </c>
       <c r="R10" t="n">
         <v>6630978</v>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,7 +1747,7 @@
         <v>132474620</v>
       </c>
       <c r="B11" t="n">
-        <v>96419</v>
+        <v>96427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>132474614</v>
       </c>
       <c r="B12" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132474615</v>
       </c>
       <c r="B13" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>132474611</v>
       </c>
       <c r="B14" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>132474626</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>132474618</v>
       </c>
       <c r="B16" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,45 +2400,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132474616</v>
+        <v>132474610</v>
       </c>
       <c r="B17" t="n">
-        <v>91892</v>
+        <v>99106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656414</v>
+        <v>656435</v>
       </c>
       <c r="R17" t="n">
-        <v>6631037</v>
+        <v>6630991</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2470,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,54 +2516,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132474610</v>
+        <v>132474616</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656435</v>
+        <v>656414</v>
       </c>
       <c r="R18" t="n">
-        <v>6630991</v>
+        <v>6631037</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2626,7 @@
         <v>132474621</v>
       </c>
       <c r="B19" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>132474628</v>
       </c>
       <c r="B20" t="n">
-        <v>106222</v>
+        <v>106230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -1302,32 +1302,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132474647</v>
+        <v>132474622</v>
       </c>
       <c r="B7" t="n">
-        <v>101312</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656483</v>
+        <v>656406</v>
       </c>
       <c r="R7" t="n">
-        <v>6630977</v>
+        <v>6631060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,7 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,32 +1414,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132474622</v>
+        <v>132474647</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>101312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656406</v>
+        <v>656483</v>
       </c>
       <c r="R8" t="n">
-        <v>6631060</v>
+        <v>6630977</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1479,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,12 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2400,54 +2400,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132474610</v>
+        <v>132474616</v>
       </c>
       <c r="B17" t="n">
-        <v>99106</v>
+        <v>91898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656435</v>
+        <v>656414</v>
       </c>
       <c r="R17" t="n">
-        <v>6630991</v>
+        <v>6631037</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,45 +2507,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132474616</v>
+        <v>132474610</v>
       </c>
       <c r="B18" t="n">
-        <v>91898</v>
+        <v>99106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656414</v>
+        <v>656435</v>
       </c>
       <c r="R18" t="n">
-        <v>6631037</v>
+        <v>6630991</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -1302,32 +1302,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132474622</v>
+        <v>132474647</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>101323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656406</v>
+        <v>656483</v>
       </c>
       <c r="R7" t="n">
-        <v>6631060</v>
+        <v>6630977</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,32 +1409,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132474647</v>
+        <v>132474622</v>
       </c>
       <c r="B8" t="n">
-        <v>101312</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656483</v>
+        <v>656406</v>
       </c>
       <c r="R8" t="n">
-        <v>6630977</v>
+        <v>6631060</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1489,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1631,7 +1631,7 @@
         <v>132474646</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>132474620</v>
       </c>
       <c r="B11" t="n">
-        <v>96427</v>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>132474614</v>
       </c>
       <c r="B12" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>132474615</v>
       </c>
       <c r="B13" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>132474611</v>
       </c>
       <c r="B14" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>132474626</v>
       </c>
       <c r="B15" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>132474618</v>
       </c>
       <c r="B16" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,45 +2400,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132474616</v>
+        <v>132474610</v>
       </c>
       <c r="B17" t="n">
-        <v>91898</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656414</v>
+        <v>656435</v>
       </c>
       <c r="R17" t="n">
-        <v>6631037</v>
+        <v>6630991</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2470,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,54 +2516,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132474610</v>
+        <v>132474616</v>
       </c>
       <c r="B18" t="n">
-        <v>99106</v>
+        <v>91908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656435</v>
+        <v>656414</v>
       </c>
       <c r="R18" t="n">
-        <v>6630991</v>
+        <v>6631037</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2626,7 @@
         <v>132474621</v>
       </c>
       <c r="B19" t="n">
-        <v>96425</v>
+        <v>96435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>132474628</v>
       </c>
       <c r="B20" t="n">
-        <v>106230</v>
+        <v>106241</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -1302,32 +1302,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132474647</v>
+        <v>132474622</v>
       </c>
       <c r="B7" t="n">
-        <v>101323</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656483</v>
+        <v>656406</v>
       </c>
       <c r="R7" t="n">
-        <v>6630977</v>
+        <v>6631060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,7 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,32 +1414,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132474622</v>
+        <v>132474647</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>101324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656406</v>
+        <v>656483</v>
       </c>
       <c r="R8" t="n">
-        <v>6631060</v>
+        <v>6630977</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1479,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,12 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,42 +1521,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132474627</v>
+        <v>132474646</v>
       </c>
       <c r="B9" t="n">
-        <v>4781</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656415</v>
+        <v>656437</v>
       </c>
       <c r="R9" t="n">
         <v>6630978</v>
@@ -1591,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,51 +1637,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132474646</v>
+        <v>132474627</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>4781</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656437</v>
+        <v>656415</v>
       </c>
       <c r="R10" t="n">
         <v>6630978</v>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,10 +1744,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132474620</v>
+        <v>132474614</v>
       </c>
       <c r="B11" t="n">
-        <v>96437</v>
+        <v>101324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2666</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656419</v>
+        <v>656401</v>
       </c>
       <c r="R11" t="n">
-        <v>6631021</v>
+        <v>6631017</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132474614</v>
+        <v>132474620</v>
       </c>
       <c r="B12" t="n">
-        <v>101323</v>
+        <v>96438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2666</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656401</v>
+        <v>656419</v>
       </c>
       <c r="R12" t="n">
-        <v>6631017</v>
+        <v>6631021</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2073,7 +2073,7 @@
         <v>132474611</v>
       </c>
       <c r="B14" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>132474626</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>132474618</v>
       </c>
       <c r="B16" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>132474610</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>132474616</v>
       </c>
       <c r="B18" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>132474621</v>
       </c>
       <c r="B19" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>132474628</v>
       </c>
       <c r="B20" t="n">
-        <v>106241</v>
+        <v>106242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>393754</v>
+        <v>132474616</v>
       </c>
       <c r="B2" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogshagen (Mora Tuna), Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656419.353734848</v>
+        <v>656414</v>
       </c>
       <c r="R2" t="n">
-        <v>6631060.039433783</v>
+        <v>6631037</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-07-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-07-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Torkade exemplar</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,77 +766,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Älrde grandominerad barrskog med mycket löv.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Elene Johansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Elene Johansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17290567</v>
+        <v>132474631</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långhundra häradsallmänning, V landsvägen, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656421.2374687076</v>
+        <v>656384</v>
       </c>
       <c r="R3" t="n">
-        <v>6631015.262132145</v>
+        <v>6630887</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,49 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17290557</v>
+        <v>393754</v>
       </c>
       <c r="B4" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -964,17 +927,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långhundra häradsallmänning, V landsvägen, Upl</t>
+          <t>Skogshagen (Mora Tuna), Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656421.2374687076</v>
+        <v>656419</v>
       </c>
       <c r="R4" t="n">
-        <v>6631015.262132145</v>
+        <v>6631060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,27 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-04-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-04-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-07-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under grov gran.</t>
+          <t>Torkade exemplar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,77 +982,78 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Blandskog med gro gran och tall</t>
+          <t>Älrde grandominerad barrskog med mycket löv.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Maria Elene Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Maria Elene Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54674433</v>
+        <v>57846406</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långhundra häradsallmänning, V landsvägen, Upl</t>
+          <t>Långhundra häradsallmänning, V landsvägen (Skogshagen), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656421.2374687076</v>
+        <v>656410</v>
       </c>
       <c r="R5" t="n">
-        <v>6631015.262132145</v>
+        <v>6631055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,22 +1080,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-08-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid foten av grov gran. Lokal 83 i Gillis Aronssons bombmurkleinventering 2007.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,13 +1099,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gammal granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1167,70 +1111,55 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Karin Martinsson, Karolin Ring</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>57846406</v>
+        <v>132474620</v>
       </c>
       <c r="B6" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1445</v>
+        <v>2666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långhundra häradsallmänning, V landsvägen (Skogshagen), Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656410.4727291409</v>
+        <v>656419</v>
       </c>
       <c r="R6" t="n">
-        <v>6631055.129798728</v>
+        <v>6631021</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,27 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-03-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-03-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid foten av grov gran. Lokal 83 i Gillis Aronssons bombmurkleinventering 2007.</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,51 +1207,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Karolin Ring</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132474622</v>
+        <v>132474621</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>96512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656406</v>
+        <v>656417</v>
       </c>
       <c r="R7" t="n">
-        <v>6631060</v>
+        <v>6631023</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132474647</v>
+        <v>132474612</v>
       </c>
       <c r="B8" t="n">
-        <v>101338</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1449,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656483</v>
+        <v>656414</v>
       </c>
       <c r="R8" t="n">
-        <v>6630977</v>
+        <v>6631000</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132474627</v>
+        <v>132474619</v>
       </c>
       <c r="B9" t="n">
-        <v>4781</v>
+        <v>96410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1556,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656415</v>
+        <v>656420</v>
       </c>
       <c r="R9" t="n">
-        <v>6630978</v>
+        <v>6631034</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,54 +1546,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132474646</v>
+        <v>132474625</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>96410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656437</v>
+        <v>656381</v>
       </c>
       <c r="R10" t="n">
-        <v>6630978</v>
+        <v>6631065</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1717,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132474614</v>
+        <v>17290557</v>
       </c>
       <c r="B11" t="n">
-        <v>101338</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,37 +1664,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Långhundra häradsallmänning, V landsvägen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656401</v>
+        <v>656421</v>
       </c>
       <c r="R11" t="n">
-        <v>6631017</v>
+        <v>6631015</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1809,22 +1728,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2015-04-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2015-04-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Under grov gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,28 +1747,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Blandskog med gro gran och tall</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132474620</v>
+        <v>132474615</v>
       </c>
       <c r="B12" t="n">
-        <v>96449</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2666</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656419</v>
+        <v>656402</v>
       </c>
       <c r="R12" t="n">
-        <v>6631021</v>
+        <v>6631028</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1921,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1851,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,14 +1883,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132474615</v>
+        <v>132474622</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1993,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656402</v>
+        <v>656406</v>
       </c>
       <c r="R13" t="n">
-        <v>6631028</v>
+        <v>6631060</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2028,7 +1953,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +1963,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2070,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132474611</v>
+        <v>132474627</v>
       </c>
       <c r="B14" t="n">
-        <v>101338</v>
+        <v>4782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,21 +2006,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656421</v>
+        <v>656415</v>
       </c>
       <c r="R14" t="n">
-        <v>6631001</v>
+        <v>6630978</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2140,7 +2065,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2075,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,57 +2102,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132474626</v>
+        <v>132474630</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>4782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656413</v>
+        <v>656373</v>
       </c>
       <c r="R15" t="n">
-        <v>6630982</v>
+        <v>6631018</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2256,7 +2172,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2182,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,45 +2209,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132474618</v>
+        <v>132474610</v>
       </c>
       <c r="B16" t="n">
-        <v>101338</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656420</v>
+        <v>656435</v>
       </c>
       <c r="R16" t="n">
-        <v>6631034</v>
+        <v>6630991</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2363,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132474610</v>
+        <v>132474626</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2355,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2444,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656435</v>
+        <v>656413</v>
       </c>
       <c r="R17" t="n">
-        <v>6630991</v>
+        <v>6630982</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2404,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2414,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,45 +2441,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132474616</v>
+        <v>132474646</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656414</v>
+        <v>656437</v>
       </c>
       <c r="R18" t="n">
-        <v>6631037</v>
+        <v>6630978</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2586,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132474621</v>
+        <v>132474628</v>
       </c>
       <c r="B19" t="n">
-        <v>96447</v>
+        <v>106324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,34 +2568,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656417</v>
+        <v>656409</v>
       </c>
       <c r="R19" t="n">
-        <v>6631023</v>
+        <v>6630987</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2693,7 +2631,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2641,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2668,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132474628</v>
+        <v>17290567</v>
       </c>
       <c r="B20" t="n">
-        <v>106258</v>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,41 +2679,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Långhundra häradsallmänning, V landsvägen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656409</v>
+        <v>656421</v>
       </c>
       <c r="R20" t="n">
-        <v>6630987</v>
+        <v>6631015</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,22 +2736,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2015-04-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2015-04-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,15 +2756,762 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132474611</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>656421</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6631001</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132474614</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>656401</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6631017</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132474618</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>656420</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6631034</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132474623</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>656386</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6631065</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132474629</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>656381</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6631009</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132474647</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>656483</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6630977</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>54674433</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långhundra häradsallmänning, V landsvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>656421</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6631015</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2015-08-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2015-08-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gammal granskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22258-2022 artfynd.xlsx
+++ b/artfynd/A 22258-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/393754</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57846406</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474621</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474612</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474619</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474625</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17290557</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1880,6 +1935,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474615</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474622</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474627</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474630</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474610</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2438,6 +2518,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474626</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2554,6 +2639,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474646</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2665,6 +2755,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474628</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2765,6 +2860,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17290567</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474611</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2979,6 +3084,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474614</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3086,6 +3196,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474618</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3193,6 +3308,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474623</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3300,6 +3420,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474629</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3407,6 +3532,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474647</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3512,8 +3642,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54674433</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>